--- a/DOC_SALESORDER_HEADER_1.xlsx
+++ b/DOC_SALESORDER_HEADER_1.xlsx
@@ -1300,7 +1300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC3"/>
+  <dimension ref="A1:BF3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13" defaultRowHeight="18" customHeight="1" outlineLevelRow="2"/>
   <cols>
     <col width="24.3008849557522" customWidth="1" style="2" min="1" max="1"/>
@@ -1319,22 +1319,32 @@
     <col width="24.0530973451327" customWidth="1" style="2" min="19" max="19"/>
     <col width="23.1858407079646" customWidth="1" style="2" min="20" max="26"/>
     <col width="22.9380530973451" customWidth="1" style="2" min="27" max="28"/>
-    <col width="12" customWidth="1" style="2" min="29" max="34"/>
+    <col width="16" customWidth="1" style="2" min="28" max="28"/>
+    <col width="20" customWidth="1" style="2" min="29" max="34"/>
+    <col width="22.9380530973451" customWidth="1" style="2" min="30" max="30"/>
+    <col width="12" customWidth="1" style="2" min="32" max="32"/>
     <col width="18.9469026548673" customWidth="1" style="2" min="35" max="35"/>
     <col width="23.1858407079646" customWidth="1" style="2" min="36" max="36"/>
     <col width="15.5752212389381" customWidth="1" style="2" min="37" max="37"/>
-    <col width="12" customWidth="1" style="2" min="38" max="39"/>
-    <col width="16.929203539823" customWidth="1" style="2" min="40" max="40"/>
+    <col width="18.9469026548673" customWidth="1" style="2" min="38" max="39"/>
+    <col width="23.1858407079646" customWidth="1" style="2" min="39" max="39"/>
+    <col width="15.5752212389381" customWidth="1" style="2" min="40" max="40"/>
     <col width="12" customWidth="1" style="2" min="41" max="41"/>
     <col width="38.6991150442478" customWidth="1" style="2" min="42" max="42"/>
-    <col width="12" customWidth="1" style="2" min="43" max="44"/>
-    <col width="12" customWidth="1" style="11" min="45" max="45"/>
+    <col width="16.929203539823" customWidth="1" style="2" min="43" max="44"/>
+    <col width="12" customWidth="1" style="2" min="44" max="44"/>
+    <col width="38.6991150442478" customWidth="1" style="11" min="45" max="45"/>
     <col width="12" customWidth="1" style="2" min="46" max="46"/>
     <col width="21.4336283185841" customWidth="1" style="2" min="47" max="47"/>
-    <col width="20.9380530973451" customWidth="1" style="2" min="48" max="48"/>
+    <col width="12" customWidth="1" style="2" min="48" max="48"/>
     <col width="12" customWidth="1" style="11" min="49" max="52"/>
+    <col width="21.4336283185841" customWidth="1" style="2" min="50" max="50"/>
+    <col width="20.9380530973451" customWidth="1" style="2" min="51" max="51"/>
+    <col width="12" customWidth="1" style="2" min="52" max="52"/>
     <col width="12" customWidth="1" style="2" min="53" max="54"/>
     <col width="20.4424778761062" customWidth="1" style="2" min="55" max="55"/>
+    <col width="12" customWidth="1" style="2" min="56" max="56"/>
+    <col width="20.4424778761062" customWidth="1" style="2" min="58" max="58"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" s="2">
@@ -1470,145 +1480,160 @@
       </c>
       <c r="AA1" s="7" t="inlineStr">
         <is>
+          <t>收货人名称</t>
+        </is>
+      </c>
+      <c r="AB1" s="7" t="inlineStr">
+        <is>
+          <t>收货联系人</t>
+        </is>
+      </c>
+      <c r="AC1" s="7" t="inlineStr">
+        <is>
+          <t>收货人电话1</t>
+        </is>
+      </c>
+      <c r="AD1" s="7" t="inlineStr">
+        <is>
           <t>收货人地址</t>
         </is>
       </c>
-      <c r="AB1" s="6" t="inlineStr">
+      <c r="AE1" s="6" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="AC1" s="6" t="inlineStr">
+      <c r="AF1" s="6" t="inlineStr">
         <is>
           <t>自定义01</t>
         </is>
       </c>
-      <c r="AD1" s="6" t="inlineStr">
+      <c r="AG1" s="6" t="inlineStr">
         <is>
           <t>自定义02</t>
         </is>
       </c>
-      <c r="AE1" s="6" t="inlineStr">
+      <c r="AH1" s="6" t="inlineStr">
         <is>
           <t>自定义03</t>
         </is>
       </c>
-      <c r="AF1" s="7" t="inlineStr">
+      <c r="AI1" s="7" t="inlineStr">
         <is>
           <t>自定义04</t>
         </is>
       </c>
-      <c r="AG1" s="7" t="inlineStr">
+      <c r="AJ1" s="7" t="inlineStr">
         <is>
           <t>自定义05</t>
         </is>
       </c>
-      <c r="AH1" s="6" t="inlineStr">
+      <c r="AK1" s="6" t="inlineStr">
         <is>
           <t>自定义06</t>
         </is>
       </c>
-      <c r="AI1" s="5" t="inlineStr">
+      <c r="AL1" s="5" t="inlineStr">
         <is>
           <t>仓库编号</t>
         </is>
       </c>
-      <c r="AJ1" s="5" t="inlineStr">
+      <c r="AM1" s="5" t="inlineStr">
         <is>
           <t>货主</t>
         </is>
       </c>
-      <c r="AK1" s="5" t="inlineStr">
+      <c r="AN1" s="5" t="inlineStr">
         <is>
           <t>产品代码</t>
         </is>
       </c>
-      <c r="AL1" s="5" t="inlineStr">
+      <c r="AO1" s="5" t="inlineStr">
         <is>
           <t>行状态</t>
         </is>
       </c>
-      <c r="AM1" s="7" t="inlineStr">
+      <c r="AP1" s="7" t="inlineStr">
         <is>
           <t>实物批次</t>
         </is>
       </c>
-      <c r="AN1" s="7" t="inlineStr">
+      <c r="AQ1" s="7" t="inlineStr">
         <is>
           <t>货物来源</t>
         </is>
       </c>
-      <c r="AO1" s="7" t="inlineStr">
+      <c r="AR1" s="7" t="inlineStr">
         <is>
           <t>库存地</t>
         </is>
       </c>
-      <c r="AP1" s="7" t="inlineStr">
+      <c r="AS1" s="7" t="inlineStr">
         <is>
           <t>质量状态</t>
         </is>
       </c>
-      <c r="AQ1" s="7" t="inlineStr">
+      <c r="AT1" s="7" t="inlineStr">
         <is>
           <t>SN</t>
         </is>
       </c>
-      <c r="AR1" s="6" t="inlineStr">
+      <c r="AU1" s="6" t="inlineStr">
         <is>
           <t>LPN</t>
         </is>
       </c>
-      <c r="AS1" s="5" t="inlineStr">
+      <c r="AV1" s="5" t="inlineStr">
         <is>
           <t>订货数</t>
         </is>
       </c>
-      <c r="AT1" s="5" t="inlineStr">
+      <c r="AW1" s="5" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
-      <c r="AU1" s="5" t="inlineStr">
+      <c r="AX1" s="5" t="inlineStr">
         <is>
           <t>预配规则</t>
         </is>
       </c>
-      <c r="AV1" s="5" t="inlineStr">
+      <c r="AY1" s="5" t="inlineStr">
         <is>
           <t>分配规则</t>
         </is>
       </c>
-      <c r="AW1" s="5" t="inlineStr">
+      <c r="AZ1" s="5" t="inlineStr">
         <is>
           <t>毛重</t>
         </is>
       </c>
-      <c r="AX1" s="5" t="inlineStr">
+      <c r="BA1" s="5" t="inlineStr">
         <is>
           <t>净重</t>
         </is>
       </c>
-      <c r="AY1" s="5" t="inlineStr">
+      <c r="BB1" s="5" t="inlineStr">
         <is>
           <t>体积</t>
         </is>
       </c>
-      <c r="AZ1" s="5" t="inlineStr">
+      <c r="BC1" s="5" t="inlineStr">
         <is>
           <t>价格</t>
         </is>
       </c>
-      <c r="BA1" s="6" t="inlineStr">
+      <c r="BD1" s="6" t="inlineStr">
         <is>
           <t>EDI相关信息1</t>
         </is>
       </c>
-      <c r="BB1" s="6" t="inlineStr">
+      <c r="BE1" s="6" t="inlineStr">
         <is>
           <t>EDI相关信息2</t>
         </is>
       </c>
-      <c r="BC1" s="6" t="inlineStr">
+      <c r="BF1" s="6" t="inlineStr">
         <is>
           <t>EDI相关信息3</t>
         </is>
@@ -1747,145 +1772,160 @@
       </c>
       <c r="AA2" s="6" t="inlineStr">
         <is>
+          <t>consigneeName</t>
+        </is>
+      </c>
+      <c r="AB2" s="6" t="inlineStr">
+        <is>
+          <t>consigneeContact</t>
+        </is>
+      </c>
+      <c r="AC2" s="6" t="inlineStr">
+        <is>
+          <t>consigneeTel1</t>
+        </is>
+      </c>
+      <c r="AD2" s="6" t="inlineStr">
+        <is>
           <t>consigneeAddress1</t>
         </is>
       </c>
-      <c r="AB2" s="6" t="inlineStr">
+      <c r="AE2" s="6" t="inlineStr">
         <is>
           <t>noteText</t>
         </is>
       </c>
-      <c r="AC2" s="6" t="inlineStr">
+      <c r="AF2" s="6" t="inlineStr">
         <is>
           <t>udf01</t>
         </is>
       </c>
-      <c r="AD2" s="6" t="inlineStr">
+      <c r="AG2" s="6" t="inlineStr">
         <is>
           <t>udf02</t>
         </is>
       </c>
-      <c r="AE2" s="6" t="inlineStr">
+      <c r="AH2" s="6" t="inlineStr">
         <is>
           <t>udf03</t>
         </is>
       </c>
-      <c r="AF2" s="6" t="inlineStr">
+      <c r="AI2" s="6" t="inlineStr">
         <is>
           <t>udf04</t>
         </is>
       </c>
-      <c r="AG2" s="6" t="inlineStr">
+      <c r="AJ2" s="6" t="inlineStr">
         <is>
           <t>udf05</t>
         </is>
       </c>
-      <c r="AH2" s="6" t="inlineStr">
+      <c r="AK2" s="6" t="inlineStr">
         <is>
           <t>udf06</t>
         </is>
       </c>
-      <c r="AI2" s="5" t="inlineStr">
+      <c r="AL2" s="5" t="inlineStr">
         <is>
           <t>D.warehouseId</t>
         </is>
       </c>
-      <c r="AJ2" s="5" t="inlineStr">
+      <c r="AM2" s="5" t="inlineStr">
         <is>
           <t>D.customerId</t>
         </is>
       </c>
-      <c r="AK2" s="5" t="inlineStr">
+      <c r="AN2" s="5" t="inlineStr">
         <is>
           <t>D.sku</t>
         </is>
       </c>
-      <c r="AL2" s="5" t="inlineStr">
+      <c r="AO2" s="5" t="inlineStr">
         <is>
           <t>D.lineStatus</t>
         </is>
       </c>
-      <c r="AM2" s="6" t="inlineStr">
+      <c r="AP2" s="6" t="inlineStr">
         <is>
           <t>D.lotAtt04</t>
         </is>
       </c>
-      <c r="AN2" s="6" t="inlineStr">
+      <c r="AQ2" s="6" t="inlineStr">
         <is>
           <t>D.lotAtt05</t>
         </is>
       </c>
-      <c r="AO2" s="6" t="inlineStr">
+      <c r="AR2" s="6" t="inlineStr">
         <is>
           <t>D.lotAtt07</t>
         </is>
       </c>
-      <c r="AP2" s="6" t="inlineStr">
+      <c r="AS2" s="6" t="inlineStr">
         <is>
           <t>D.lotAtt08</t>
         </is>
       </c>
-      <c r="AQ2" s="6" t="inlineStr">
+      <c r="AT2" s="6" t="inlineStr">
         <is>
           <t>D.lotAtt09</t>
         </is>
       </c>
-      <c r="AR2" s="6" t="inlineStr">
+      <c r="AU2" s="6" t="inlineStr">
         <is>
           <t>D.lotAtt11</t>
         </is>
       </c>
-      <c r="AS2" s="5" t="inlineStr">
+      <c r="AV2" s="5" t="inlineStr">
         <is>
           <t>D.qtyOrdered</t>
         </is>
       </c>
-      <c r="AT2" s="5" t="inlineStr">
+      <c r="AW2" s="5" t="inlineStr">
         <is>
           <t>D.uom</t>
         </is>
       </c>
-      <c r="AU2" s="5" t="inlineStr">
+      <c r="AX2" s="5" t="inlineStr">
         <is>
           <t>D.softAllocationRule</t>
         </is>
       </c>
-      <c r="AV2" s="5" t="inlineStr">
+      <c r="AY2" s="5" t="inlineStr">
         <is>
           <t>D.allocationRule</t>
         </is>
       </c>
-      <c r="AW2" s="5" t="inlineStr">
+      <c r="AZ2" s="5" t="inlineStr">
         <is>
           <t>D.grossWeight</t>
         </is>
       </c>
-      <c r="AX2" s="5" t="inlineStr">
+      <c r="BA2" s="5" t="inlineStr">
         <is>
           <t>D.netWeight</t>
         </is>
       </c>
-      <c r="AY2" s="5" t="inlineStr">
+      <c r="BB2" s="5" t="inlineStr">
         <is>
           <t>D.cubic</t>
         </is>
       </c>
-      <c r="AZ2" s="5" t="inlineStr">
+      <c r="BC2" s="5" t="inlineStr">
         <is>
           <t>D.price</t>
         </is>
       </c>
-      <c r="BA2" s="6" t="inlineStr">
+      <c r="BD2" s="6" t="inlineStr">
         <is>
           <t>D.dedi01</t>
         </is>
       </c>
-      <c r="BB2" s="6" t="inlineStr">
+      <c r="BE2" s="6" t="inlineStr">
         <is>
           <t>D.dedi02</t>
         </is>
       </c>
-      <c r="BC2" s="6" t="inlineStr">
+      <c r="BF2" s="6" t="inlineStr">
         <is>
           <t>D.dedi03</t>
         </is>
@@ -1961,21 +2001,9 @@
       <c r="S3" s="0" t="n"/>
       <c r="T3" s="0" t="n"/>
       <c r="U3" s="0" t="n"/>
-      <c r="V3" s="0" t="inlineStr">
-        <is>
-          <t>供应商</t>
-        </is>
-      </c>
-      <c r="W3" s="0" t="inlineStr">
-        <is>
-          <t>收货人</t>
-        </is>
-      </c>
-      <c r="X3" s="0" t="inlineStr">
-        <is>
-          <t>收货人电话</t>
-        </is>
-      </c>
+      <c r="V3" s="0" t="n"/>
+      <c r="W3" s="0" t="n"/>
+      <c r="X3" s="0" t="n"/>
       <c r="Y3" s="0" t="n"/>
       <c r="Z3" s="0" t="inlineStr">
         <is>
@@ -1984,109 +2012,124 @@
       </c>
       <c r="AA3" s="0" t="inlineStr">
         <is>
+          <t>供应商</t>
+        </is>
+      </c>
+      <c r="AB3" s="0" t="inlineStr">
+        <is>
+          <t>收货人</t>
+        </is>
+      </c>
+      <c r="AC3" s="0" t="inlineStr">
+        <is>
+          <t>收货人电话</t>
+        </is>
+      </c>
+      <c r="AD3" s="0" t="inlineStr">
+        <is>
           <t>收货地址</t>
         </is>
       </c>
-      <c r="AB3" s="0" t="inlineStr">
+      <c r="AE3" s="0" t="inlineStr">
         <is>
           <t>申请说明</t>
         </is>
       </c>
-      <c r="AC3" s="0" t="inlineStr"/>
-      <c r="AD3" s="0" t="inlineStr"/>
-      <c r="AE3" s="0" t="inlineStr"/>
       <c r="AF3" s="0" t="inlineStr"/>
       <c r="AG3" s="0" t="inlineStr"/>
       <c r="AH3" s="0" t="inlineStr"/>
-      <c r="AI3" s="0" t="inlineStr">
+      <c r="AI3" s="0" t="inlineStr"/>
+      <c r="AJ3" s="0" t="inlineStr"/>
+      <c r="AK3" s="0" t="inlineStr"/>
+      <c r="AL3" s="0" t="inlineStr">
         <is>
           <t>固定值WH004078</t>
         </is>
       </c>
-      <c r="AJ3" s="0" t="inlineStr">
+      <c r="AM3" s="0" t="inlineStr">
         <is>
           <t>固定值GEHC</t>
         </is>
       </c>
-      <c r="AK3" s="0" t="inlineStr">
+      <c r="AN3" s="0" t="inlineStr">
         <is>
           <t>物料编号</t>
         </is>
       </c>
-      <c r="AL3" s="10" t="inlineStr">
+      <c r="AO3" s="10" t="inlineStr">
         <is>
           <t>固定值00</t>
         </is>
       </c>
-      <c r="AM3" s="0" t="n"/>
-      <c r="AN3" s="0" t="inlineStr">
+      <c r="AP3" s="0" t="n"/>
+      <c r="AQ3" s="0" t="inlineStr">
         <is>
           <t>固定值OSCAR</t>
         </is>
       </c>
-      <c r="AO3" s="0" t="inlineStr">
+      <c r="AR3" s="0" t="inlineStr">
         <is>
           <t>仓库</t>
         </is>
       </c>
-      <c r="AP3" s="0" t="inlineStr">
+      <c r="AS3" s="0" t="inlineStr">
         <is>
           <t>状态为好件时候则为GOOD 其余情况置空</t>
         </is>
       </c>
-      <c r="AQ3" s="0" t="inlineStr">
+      <c r="AT3" s="0" t="inlineStr">
         <is>
           <t>序列号</t>
         </is>
       </c>
-      <c r="AR3" s="0" t="n"/>
-      <c r="AS3" s="0" t="inlineStr">
+      <c r="AU3" s="0" t="n"/>
+      <c r="AV3" s="0" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="AT3" s="0" t="inlineStr">
+      <c r="AW3" s="0" t="inlineStr">
         <is>
           <t>固定值EA</t>
         </is>
       </c>
-      <c r="AU3" s="0" t="inlineStr">
+      <c r="AX3" s="0" t="inlineStr">
         <is>
           <t>固定值HD78_E841_01</t>
         </is>
       </c>
-      <c r="AV3" s="0" t="inlineStr">
+      <c r="AY3" s="0" t="inlineStr">
         <is>
           <t>固定值HD78_E841_01</t>
         </is>
       </c>
-      <c r="AW3" s="0" t="inlineStr">
+      <c r="AZ3" s="0" t="inlineStr">
         <is>
           <t>固定值0</t>
         </is>
       </c>
-      <c r="AX3" s="0" t="inlineStr">
+      <c r="BA3" s="0" t="inlineStr">
         <is>
           <t>固定值0</t>
         </is>
       </c>
-      <c r="AY3" s="0" t="inlineStr">
+      <c r="BB3" s="0" t="inlineStr">
         <is>
           <t>固定值0</t>
         </is>
       </c>
-      <c r="AZ3" s="0" t="inlineStr">
+      <c r="BC3" s="0" t="inlineStr">
         <is>
           <t>固定值0</t>
         </is>
       </c>
-      <c r="BA3" s="0" t="n"/>
-      <c r="BB3" s="0" t="inlineStr">
+      <c r="BD3" s="0" t="n"/>
+      <c r="BE3" s="0" t="inlineStr">
         <is>
           <t>跟踪号</t>
         </is>
       </c>
-      <c r="BC3" s="0" t="inlineStr">
+      <c r="BF3" s="0" t="inlineStr">
         <is>
           <t>货位</t>
         </is>
